--- a/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Metal ETF.xlsx
+++ b/data/data/ICICI Prudential Mutual Fund/ICICI Prudential Nifty Metal ETF.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\Feb\Portfolio stage 8\Riskometer updated Portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\mumchfnp01\RatingFinance\Factseet Mandates\ICICI PRUDENTIAL FACTSHEET\2025\June\Portfolio stage 8\Riskometer updated portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA241EA-F39C-40EF-9DA6-7166C67A58F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF736A9-4A74-4B0C-BCFE-56A2D62239A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
     <t>ICICI Prudential Nifty Metal ETF</t>
   </si>
   <si>
-    <t>Portfolio as on Jan 31,2025</t>
+    <t>Portfolio as on May 31,2025</t>
   </si>
   <si>
     <t>Company/Issuer/Instrument Name</t>
@@ -139,24 +139,30 @@
     <t>INE220G01021</t>
   </si>
   <si>
+    <t>Steel Authority Of India Ltd.</t>
+  </si>
+  <si>
+    <t>INE114A01011</t>
+  </si>
+  <si>
+    <t>Lloyds Metals &amp; Energy Ltd.</t>
+  </si>
+  <si>
+    <t>INE281B01032</t>
+  </si>
+  <si>
+    <t>Hindustan Zinc Ltd.</t>
+  </si>
+  <si>
+    <t>INE267A01025</t>
+  </si>
+  <si>
     <t>National Aluminium Company Ltd.</t>
   </si>
   <si>
     <t>INE139A01034</t>
   </si>
   <si>
-    <t>Steel Authority Of India Ltd.</t>
-  </si>
-  <si>
-    <t>INE114A01011</t>
-  </si>
-  <si>
-    <t>Hindustan Zinc Ltd.</t>
-  </si>
-  <si>
-    <t>INE267A01025</t>
-  </si>
-  <si>
     <t>Welspun Corp Ltd.</t>
   </si>
   <si>
@@ -169,12 +175,6 @@
     <t>INE531E01026</t>
   </si>
   <si>
-    <t>Ratnamani Metals &amp; Tubes Ltd.</t>
-  </si>
-  <si>
-    <t>INE703B01027</t>
-  </si>
-  <si>
     <t>Unlisted</t>
   </si>
   <si>
@@ -232,7 +232,7 @@
     <t>@ As per AMFI Best Practices Guidelines Circular No. 91/ 2020 - 21 dated March 24, 2021 on Valuation of AT-1 Bonds and Tier 2 Bonds, Yield to call is disclosed for AT-1 Bonds and Tier 2 Bonds issued by Banks as provided by Valuation agencies.</t>
   </si>
   <si>
-    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2023/74 dated May 19, 2023.Refer link: https://www.icicipruamc.com/statutory-disclosures/deviation-in-valuation-of-securities</t>
+    <t>For Instances of Deviation In valuation Of Securities as per SEBI master circular ref no SEBI/HO/IMD/IMD-PoD-1/P/CIR/2024/90 dated June 27, 2024. Refer link: https://www.icicipruamc.com/about-us/statutory-disclosures?currentTabFilter=OtherDisclosures&amp;&amp;subCatTabFilter=deviationinvaluationofsecurities</t>
   </si>
   <si>
     <t>As per AMFI Best Practices Guidelines Circular No. AMFI/ 35P/ MEM-COR/ 72 / 2022-23 dated December 31, 2022 on Standard format for disclosure Portfolio YTM for Debt Schemes, Yield of the instrument is disclosed on annualized basis as provided by Valuation agencies.</t>
@@ -1056,10 +1056,10 @@
         <v>13</v>
       </c>
       <c r="G5" s="12">
-        <v>12194.280000000002</v>
+        <v>15730.980000000003</v>
       </c>
       <c r="H5" s="13">
-        <v>0.99997633043710021</v>
+        <v>0.99996410688039994</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>13</v>
@@ -1093,10 +1093,10 @@
         <v>13</v>
       </c>
       <c r="G7" s="12">
-        <v>12194.280000000002</v>
+        <v>15730.980000000003</v>
       </c>
       <c r="H7" s="13">
-        <v>0.99997633043710021</v>
+        <v>0.99996410688039994</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>13</v>
@@ -1119,13 +1119,13 @@
         <v>17</v>
       </c>
       <c r="F8" s="17">
-        <v>1701799</v>
+        <v>1965090</v>
       </c>
       <c r="G8" s="18">
-        <v>2290.96</v>
+        <v>3164.19</v>
       </c>
       <c r="H8" s="19">
-        <v>0.1878672438208</v>
+        <v>0.2011366378542</v>
       </c>
       <c r="I8" s="18" t="s">
         <v>13</v>
@@ -1148,13 +1148,13 @@
         <v>17</v>
       </c>
       <c r="F9" s="17">
-        <v>197090</v>
+        <v>225470</v>
       </c>
       <c r="G9" s="18">
-        <v>1862.5</v>
+        <v>2240.04</v>
       </c>
       <c r="H9" s="19">
-        <v>0.15273192967849999</v>
+        <v>0.1423916118371</v>
       </c>
       <c r="I9" s="18" t="s">
         <v>13</v>
@@ -1177,13 +1177,13 @@
         <v>22</v>
       </c>
       <c r="F10" s="17">
-        <v>298551</v>
+        <v>344066</v>
       </c>
       <c r="G10" s="18">
-        <v>1774.29</v>
+        <v>2179.66</v>
       </c>
       <c r="H10" s="19">
-        <v>0.14549838148149999</v>
+        <v>0.13855346362429999</v>
       </c>
       <c r="I10" s="18" t="s">
         <v>13</v>
@@ -1206,13 +1206,13 @@
         <v>25</v>
       </c>
       <c r="F11" s="17">
-        <v>348158</v>
+        <v>403247</v>
       </c>
       <c r="G11" s="18">
-        <v>1536.77</v>
+        <v>1756.34</v>
       </c>
       <c r="H11" s="19">
-        <v>0.1260208577568</v>
+        <v>0.1116444722121</v>
       </c>
       <c r="I11" s="18" t="s">
         <v>13</v>
@@ -1235,13 +1235,13 @@
         <v>28</v>
       </c>
       <c r="F12" s="17">
-        <v>51119</v>
+        <v>61896</v>
       </c>
       <c r="G12" s="18">
-        <v>1169.5</v>
+        <v>1559.72</v>
       </c>
       <c r="H12" s="19">
-        <v>9.5903351279999993E-2</v>
+        <v>9.9146017399000003E-2</v>
       </c>
       <c r="I12" s="18" t="s">
         <v>13</v>
@@ -1264,13 +1264,13 @@
         <v>17</v>
       </c>
       <c r="F13" s="17">
-        <v>77922</v>
+        <v>90292</v>
       </c>
       <c r="G13" s="18">
-        <v>616.79</v>
+        <v>856.78</v>
       </c>
       <c r="H13" s="19">
-        <v>5.0579074848999997E-2</v>
+        <v>5.4462547628500002E-2</v>
       </c>
       <c r="I13" s="18" t="s">
         <v>13</v>
@@ -1293,13 +1293,13 @@
         <v>33</v>
       </c>
       <c r="F14" s="17">
-        <v>37122</v>
+        <v>43047</v>
       </c>
       <c r="G14" s="18">
-        <v>560.38</v>
+        <v>779.88</v>
       </c>
       <c r="H14" s="19">
-        <v>4.59532449681E-2</v>
+        <v>4.9574280030499997E-2</v>
       </c>
       <c r="I14" s="18" t="s">
         <v>13</v>
@@ -1322,13 +1322,13 @@
         <v>36</v>
       </c>
       <c r="F15" s="17">
-        <v>708883</v>
+        <v>821314</v>
       </c>
       <c r="G15" s="18">
-        <v>468.57</v>
+        <v>584.53</v>
       </c>
       <c r="H15" s="19">
-        <v>3.84244833769E-2</v>
+        <v>3.7156554734299997E-2</v>
       </c>
       <c r="I15" s="18" t="s">
         <v>13</v>
@@ -1351,13 +1351,13 @@
         <v>17</v>
       </c>
       <c r="F16" s="17">
-        <v>66915</v>
+        <v>77021</v>
       </c>
       <c r="G16" s="18">
-        <v>437.16</v>
+        <v>496.59</v>
       </c>
       <c r="H16" s="19">
-        <v>3.5848746511799999E-2</v>
+        <v>3.1566512438200002E-2</v>
       </c>
       <c r="I16" s="18" t="s">
         <v>13</v>
@@ -1377,16 +1377,16 @@
         <v>13</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F17" s="17">
-        <v>183932</v>
+        <v>343525</v>
       </c>
       <c r="G17" s="18">
-        <v>371.98</v>
+        <v>443.77</v>
       </c>
       <c r="H17" s="19">
-        <v>3.0503744000900002E-2</v>
+        <v>2.82089273338E-2</v>
       </c>
       <c r="I17" s="18" t="s">
         <v>13</v>
@@ -1406,16 +1406,16 @@
         <v>13</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F18" s="17">
-        <v>296494</v>
+        <v>28888</v>
       </c>
       <c r="G18" s="18">
-        <v>318.52</v>
+        <v>402.44</v>
       </c>
       <c r="H18" s="19">
-        <v>2.6119825095899999E-2</v>
+        <v>2.5581721874399999E-2</v>
       </c>
       <c r="I18" s="18" t="s">
         <v>13</v>
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="F19" s="17">
-        <v>61156</v>
+        <v>87137</v>
       </c>
       <c r="G19" s="18">
-        <v>275.29000000000002</v>
+        <v>399.26</v>
       </c>
       <c r="H19" s="19">
-        <v>2.25748042529E-2</v>
+        <v>2.5379580249499999E-2</v>
       </c>
       <c r="I19" s="18" t="s">
         <v>13</v>
@@ -1464,16 +1464,16 @@
         <v>13</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F20" s="17">
-        <v>26795</v>
+        <v>213101</v>
       </c>
       <c r="G20" s="18">
-        <v>198.82</v>
+        <v>384.33</v>
       </c>
       <c r="H20" s="19">
-        <v>1.63039797362E-2</v>
+        <v>2.44305316768E-2</v>
       </c>
       <c r="I20" s="18" t="s">
         <v>13</v>
@@ -1493,16 +1493,16 @@
         <v>13</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F21" s="17">
-        <v>67326</v>
+        <v>31044</v>
       </c>
       <c r="G21" s="18">
-        <v>160.9</v>
+        <v>290.43</v>
       </c>
       <c r="H21" s="19">
-        <v>1.31943986498E-2</v>
+        <v>1.8461632750200001E-2</v>
       </c>
       <c r="I21" s="18" t="s">
         <v>13</v>
@@ -1522,16 +1522,16 @@
         <v>13</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F22" s="17">
-        <v>5312</v>
+        <v>77983</v>
       </c>
       <c r="G22" s="18">
-        <v>151.85</v>
+        <v>193.02</v>
       </c>
       <c r="H22" s="19">
-        <v>1.2452264978E-2</v>
+        <v>1.22696152375E-2</v>
       </c>
       <c r="I22" s="18" t="s">
         <v>13</v>
@@ -2046,10 +2046,10 @@
         <v>13</v>
       </c>
       <c r="G50" s="12">
-        <v>7.79</v>
+        <v>113.86</v>
       </c>
       <c r="H50" s="13">
-        <v>6.3880898369999997E-4</v>
+        <v>7.2376872394000003E-3</v>
       </c>
       <c r="I50" s="12" t="s">
         <v>13</v>
@@ -2083,10 +2083,10 @@
         <v>13</v>
       </c>
       <c r="G52" s="21">
-        <v>-7.5013599000012618</v>
+        <v>-113.29534580000109</v>
       </c>
       <c r="H52" s="22">
-        <v>-6.1513942160562943E-4</v>
+        <v>-7.2017941206907196E-3</v>
       </c>
       <c r="I52" s="21" t="s">
         <v>13</v>
@@ -2112,10 +2112,10 @@
         <v>13</v>
       </c>
       <c r="G53" s="21">
-        <v>12194.5686401</v>
+        <v>15731.544654200001</v>
       </c>
       <c r="H53" s="22">
-        <v>0.99999999999919464</v>
+        <v>0.99999999999910938</v>
       </c>
       <c r="I53" s="21" t="s">
         <v>13</v>
